--- a/商品选品表格模板.xlsx
+++ b/商品选品表格模板.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品选品台" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'商品选品台'!$A$1:$L$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'商品选品台'!$A$1:$M$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -192,30 +192,35 @@
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
+        <t>填写商品在对应节点或榜单周期内的真实广告消耗金额，仅填写数字；节点榜单将按此字段降序展示 Top 25。</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
         <t>填写 ROI 数值，例如 1.70。</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>填写百分比数值，例如 4.89 表示 4.89%。</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>填写百分比数值，例如 9.73 表示 9.73%。</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>填写可访问的视频或图片素材链接。</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <t>填写落地页 URL 或小程序口令。</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>填写数据创建日期。</t>
       </text>
@@ -225,7 +230,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SelectionTemplate" displayName="SelectionTemplate" ref="A1:L3" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SelectionTemplate" displayName="SelectionTemplate" ref="A1:M3" headerRowCount="1">
   <autoFilter ref="A1:L3"/>
   <tableColumns count="12">
     <tableColumn id="1" name="开户行业"/>
@@ -534,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -543,7 +548,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="45" customWidth="1" min="10" max="10"/>
@@ -584,30 +589,35 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>消耗(元)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>ROI</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>CTR</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>CVR</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>素材链接</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>落地页链接（复制到微信点击查看）</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>创建日期</t>
         </is>
@@ -638,26 +648,26 @@
           <t>视频号</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>1.7</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>4.89</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="J2" s="2" t="n">
         <v>9.73</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>https://example.com/material.mp4</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>#小程序://示例商城/请替换真实链路</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>2026年7月20日</t>
         </is>
@@ -688,33 +698,33 @@
           <t>视频号</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>1.68</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="I3" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="J3" s="2" t="n">
         <v>16.22</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>https://example.com/material-2.mp4</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>#小程序://示例商城/请替换真实链路</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>2026年7月20日</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:M3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
